--- a/www/download/COUNTRY.WME.EXI382.xlsx
+++ b/www/download/COUNTRY.WME.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,11 @@
           <t>Country</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Resto do mundo - Oriente Medio</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -505,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -962,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1827</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>44.74</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>19.412</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>19.676</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>20.43</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>20.668</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>20.902</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>19.46</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>21.312</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>23.276</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>25.283</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>26.457</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>27.778</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>31.412</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>34.685</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>35.388</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>36.985</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>38.411</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>38.706</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>39.17</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>36.8</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>34.862</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>38.19</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>37.361</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>37.248</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>37.591</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>41.006</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>42.729</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>28.688</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>7.84</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>8.194</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>14.265</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>8.292</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>14.785</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>13.358</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>14.83</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>15.889</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>17.163</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>18.043</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>18.441</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>20.264</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>22.946</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>23.957</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>24.56</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>26.508</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>27.381</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>28.029</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>26.144</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>24.956</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>26.485</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>25.907</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>25.784</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>25.931</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>27.467</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>28.541</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>116851.919</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>52254</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>52922</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>54506</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>55142</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>55951</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>51432</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>57255</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>61680</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>67064</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>72206</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>74872</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>87939</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>93569</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>92014</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>99306</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>101400</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>102375</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>104591</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>98166.866</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>93174.021</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>101909.567</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>100128.783</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>99892.368</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>100251.706</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>108258.277</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>112688.485</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>77892.274</t>
+          <t>160385751924.862</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>21246</t>
+          <t>64093997543.0552</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>70871892580.5334</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>22380</t>
+          <t>73761578826.0267</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22908</t>
+          <t>78477248281.556</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23769</t>
+          <t>87038886967.4174</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20508</t>
+          <t>97204349652.363</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>23137</t>
+          <t>105290428302.277</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>23772</t>
+          <t>100812445903.663</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>25638</t>
+          <t>118423010897.911</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>124385495058.347</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>135876964224.222</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>29199</t>
+          <t>145944223222.989</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>34463</t>
+          <t>174289034553.502</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>36474</t>
+          <t>168728605042.787</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>172484830126.364</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>42100</t>
+          <t>181319709966.183</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>46073</t>
+          <t>194079804102.094</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>49031</t>
+          <t>195531466886.947</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>71800.384</t>
+          <t>180036790283.691</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>68839.622</t>
+          <t>168994120867.219</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>73439.718</t>
+          <t>171030626821.473</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>71921.899</t>
+          <t>171510551148.541</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>71614.043</t>
+          <t>172954292794.93</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>71455.053</t>
+          <t>167158795527.744</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>75213.365</t>
+          <t>190882422278.749</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>77972.882</t>
+          <t>192812872948.639</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>57855977923.7905</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>19531202166.051</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>25152254152.6868</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>26488764553.1489</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>29903347212.6206</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>37261702466.9155</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>36755518576.6107</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>44989506085.9004</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>42541312149.6395</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>51974057066.3519</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>56760150450.255</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>60236733968.0932</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>55917419546.1481</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>71591794725.5758</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>69633311754.5179</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>66639038599.486</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>70083513325.3025</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>76965300733.3512</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>83091571593.6319</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>71042690112.6722</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>68341256077.8667</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>76022527162.067</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>79512605231.625</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>84542222450.9233</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>78113558533.055</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>90909492687.6348</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>91016206784.9022</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3913055225827.23</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>11329019.6412354</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>10626235.7567354</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>11166768.2926749</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>11232246.7020378</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>8945115.06476258</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9337321.89041161</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>10323423.1771099</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>11219312.1796562</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>12257824.8313415</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>10485083.9362408</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>10862659.2034018</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>10363195.1433072</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>10726845.9970379</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>11119382.8117938</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>8521419.58457973</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>7680783.92713408</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>7832324.05498445</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>7599133.24824</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>434876279872.915</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>360818839759.062</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>433084253965.909</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>441028335418.145</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>444938233901.19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>384736657097.922</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>430472407206.996</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>429231362443.2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>270224.344206485</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>233675.001020081</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>256235.849058038</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>266666.789317064</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>271723.980036801</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>339911.596204482</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>332519.005281281</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>388878.030827046</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>359980.25601565</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>389537.151183601</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>446231.86680783</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>515483.103710161</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>622956.58668909</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>665509.103283279</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>665348.612195092</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>812554.933118717</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>844554.253928744</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>933594.77305766</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>942011.262049535</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>913053.297442521</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>972988.941649571</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>902644.182590126</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>935057.395439721</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>925682.449362454</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1020665.99557454</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>1061070.01974121</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1083016.30518616</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>597854.352539935</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>487054.92963404</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>586580.008393422</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>627632.923837718</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>704356.442068736</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>933823.982866502</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1047158.30177874</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1099509.69176549</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>967071.771201762</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1110147.2536193</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1250045.83765508</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1460719.47387172</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1625513.93695664</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1950557.39094927</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1892316.46335225</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2230808.3570227</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2441344.92357823</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2884287.72505656</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2838526.24729137</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2705275.81042281</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2868531.0732098</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2646089.69970649</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2805413.63238542</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>2751435.53142434</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2833319.97664156</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>3077875.41377187</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>3052355.06634999</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.346313329492119</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.0877978641240849</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.115705500390572</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.155113483866076</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.233931912802006</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.362106441027692</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.442042969486496</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.485724516383136</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.441202003445677</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.506715437525402</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.509761694088889</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.562658891599863</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-0.477819251371504</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-0.518618018557861</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-0.476198976021612</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.44326927909384</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-0.399288106397256</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-0.401379588450823</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-0.409916083428638</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.0106653371232268</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.00729231488432447</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>-0.0339742633770209</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>-0.0954654491527126</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>-0.152919802309313</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>-0.0852413606836741</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>-0.172656638613427</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>-0.143307712325408</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2016.72183107011</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2491.16121605058</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3069.48173153152</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1856.90603246799</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3606.20187798096</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2520.30507872599</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2751.51168760949</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>3033.72304993213</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2677.38966647736</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>3028.24414391016</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>3145.79179138077</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>3266.42159773043</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2759.48713937537</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>3120.05276481199</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2906.65630432165</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2713.33799947419</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2643.87270682714</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2810.9222788725</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2964.48576808348</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2717.33109098624</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2738.44118206012</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2870.4323885504</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>3069.12251034633</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>3278.8316859338</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>3012.38643734115</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>3309.8187496077</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>3189.00897197748</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>36462944140.6531</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>15154413995.3773</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>23307400733.0286</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>16866291992.569</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>33496984486.1048</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>52891540346.4624</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>56035647088.1122</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>55779127202.4752</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>51137736292.7969</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>69567429803.1559</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>82250751284.2919</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>87002320120.187</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>67093600636.6607</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>104135033013.396</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>76503489727.5112</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>82010491761.797</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>108378111875.308</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.069</t>
+          <t>118296141312.349</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>122333849538.275</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.055</t>
+          <t>100638689730.387</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.186</t>
+          <t>74558900887.875</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1.203</t>
+          <t>77530416624.9906</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>92217087162.3344</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.256</t>
+          <t>105504249929.224</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.434</t>
+          <t>94602456882.2656</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>106481806589.423</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1.517</t>
+          <t>104466059172.715</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>39603498885.4193</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>16313855565.788</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>25014118726.4055</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>18994090608.6413</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>34536738534.297</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>53353813593.5164</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>53461314055.1854</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>51083863740.871</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>47209097938.8306</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>61832921094.0566</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>74766834117.1341</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>78990774606.744</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>61336748563.2911</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>93535451408.8613</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>80536620214.1709</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>86075567488.9633</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>110906525518.521</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>121184692628.447</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>125116596761.503</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>103183387923.224</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>76099637343.2848</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>80416660409.1646</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>87488806873.26</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>101673207885.459</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>91445315943.0667</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>102798987505.823</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>103889268980.75</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-3140554744.76627</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-1159441570.41072</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-1706717993.37685</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-2127798616.07224</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-1039754048.1922</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-462273247.054052</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2574333032.92673</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>4695263461.60421</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>3928638353.96628</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>7734508709.09933</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>7483917167.15782</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>8011545513.44301</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>5756852073.36958</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>10599581604.5343</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-4033130486.65979</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-4065075727.16635</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-2528413643.21378</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-2888551316.0984</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-2782747223.22749</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-2544698192.8364</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-1540736455.40981</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-2886243784.17399</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>4728280289.07441</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>3831042043.76491</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>3157140939.19893</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>3682819083.59924</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>576790191.965839</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>2715.13948304744</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.897</t>
+          <t>2709.87985000858</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.029</t>
+          <t>2714.32581184495</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>1568.87486855995</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>2762.59617471468</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1607.68637636451</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1535.22529064179</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1560.16938866347</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1496.11998162279</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.453</t>
+          <t>1493.78608759499</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.754</t>
+          <t>1542.18763855559</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2.044</t>
+          <t>1428.54044205357</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.275</t>
+          <t>1440.95106026974</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.628</t>
+          <t>1501.93718212922</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.535</t>
+          <t>1522.50954855692</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>3.088</t>
+          <t>1510.59862050934</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>3.629</t>
+          <t>1588.20578016274</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>4.147</t>
+          <t>1682.67545141141</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>4.005</t>
+          <t>1749.29537265076</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3.951</t>
+          <t>2746.31234314704</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>4.253</t>
+          <t>2758.4107574519</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>4.298</t>
+          <t>2772.91156257586</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>4.434</t>
+          <t>2776.12735139142</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>4.616</t>
+          <t>2777.4333927153</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>5.057</t>
+          <t>2755.60651851714</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>5.341</t>
+          <t>2738.35656988074</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>5.442</t>
+          <t>2731.99939161818</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>2611.78907828571</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>2691.81236542152</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>2689.63168888504</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>2667.93930494442</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>2667.96334465457</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>2676.87641137601</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>2642.91917390677</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>2686.53985116125</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>2649.92846739813</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>2652.52283145639</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>2729.16257200281</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>2695.35103066419</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>2799.5619466633</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>2697.70244517058</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>2600.18368067799</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>2685.04899310081</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>2639.87566029274</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.069</t>
+          <t>2644.95243606933</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>2670.18126116942</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1.055</t>
+          <t>2667.56537732746</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>1.186</t>
+          <t>2672.65796068181</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>1.203</t>
+          <t>2668.5150860658</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>2680.06151635248</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1.256</t>
+          <t>2681.81149645888</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1.434</t>
+          <t>2666.87224801404</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>2640.08450678252</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1.517</t>
+          <t>2637.26297076959</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>163252.405288187</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>212467.051272485</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>246504.91065798</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>201396.838221243</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>267023.010356825</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>417538.739614148</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>397780.122429388</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>397751.489299891</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>389301.579880177</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>457554.000060848</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>612999.581511819</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>730389.050187021</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>749074.132437174</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>899712.334167094</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>716088.938219887</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>941764.085296522</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1221870.57928346</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1447175.91010362</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>1377027.39281239</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1254398.41561066</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>1124776.2475722</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>1056210.11315535</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>1187302.41722188</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>1315764.98269309</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>1288091.00239874</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>1361393.70183531</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1429819.17191727</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>27208808135.2717</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>12014515237.7869</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>13926614647.3447</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>14320428201.0407</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>17177700968.1239</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>21737130223.0565</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>23776425487.3675</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>26203298960.9953</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>25344614162.0262</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>30632505996.009</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>35476403526.7918</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>36316806700.1645</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>35547961901.8886</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>43693562320.6084</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>48190115276.0715</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>51919169040.3498</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>54272531188.907</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>63514641785.4721</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>64596252726.3126</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>56225262943.4203</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>51813106949.6483</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>49589692026.4569</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>51922390818.4207</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>53216566122.4616</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>48307913147.3922</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>53430557808.9092</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>56584184827.9252</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>170929.107741399</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>209322.875027342</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>246482.610628332</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>239060.825137923</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>252878.778296914</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>318383.665043693</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>327015.490507157</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>340298.557753439</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>319515.474814337</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>372779.037870416</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>452388.339291671</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>548695.929124637</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>619791.07425129</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>696644.217469954</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>697632.207944056</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>825488.446195554</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>887884.452792995</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1110778.93968653</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1082573.78731635</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1055575.01896375</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>1137931.58896034</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>1131034.82718232</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>1171929.28286831</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>1165387.03451828</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>1219567.57148626</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>1266689.12915468</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1307923.8267225</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>116851.919</t>
+          <t>68020805650.0262</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>52254</t>
+          <t>26530227405.5895</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>52922</t>
+          <t>37229841088.7303</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>54506</t>
+          <t>38282552073.0446</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>55142</t>
+          <t>48080012463.6962</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>55951</t>
+          <t>59245694951.2498</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>51432</t>
+          <t>68399224313.3732</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>57255</t>
+          <t>72368623126.9176</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>61680</t>
+          <t>64627250428.5573</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>67064</t>
+          <t>84653068907.2039</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>72206</t>
+          <t>90864830701.93</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>74872</t>
+          <t>96284698532.923</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>87939</t>
+          <t>86586881574.2207</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>93569</t>
+          <t>120000272728.369</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>92014</t>
+          <t>121976932850.582</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>99306</t>
+          <t>119592640044.572</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>101400</t>
+          <t>124136780625.914</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>102375</t>
+          <t>145133007125.255</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>104591</t>
+          <t>153199394440.056</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>98166.866</t>
+          <t>135727814270.434</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>93174.021</t>
+          <t>127643667378.924</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>101909.567</t>
+          <t>135055758309.662</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>100128.783</t>
+          <t>142658695295.733</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>99892.368</t>
+          <t>143774795970.415</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>100251.706</t>
+          <t>136656414233.369</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>108258.277</t>
+          <t>150722107046.685</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>112688.485</t>
+          <t>149173362023.049</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>77892.274</t>
+          <t>-7676.70245321168</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21246</t>
+          <t>3144.17624514227</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>22.3000296481371</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>22380</t>
+          <t>-37663.9869166801</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22908</t>
+          <t>14144.2320599108</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>23769</t>
+          <t>99155.0745704545</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20508</t>
+          <t>70764.6319222309</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>23137</t>
+          <t>57452.931546452</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>23772</t>
+          <t>69786.1050658404</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>25638</t>
+          <t>84774.9621904314</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>160611.242220148</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>181693.121062385</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>29199</t>
+          <t>129283.058185884</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>34463</t>
+          <t>203068.11669714</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>36474</t>
+          <t>18456.7302758314</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>116275.639100968</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>42100</t>
+          <t>333986.126490464</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>46073</t>
+          <t>336396.970417088</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>49031</t>
+          <t>294453.605496039</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>71800.384</t>
+          <t>198823.396646912</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>68839.622</t>
+          <t>-13155.3413881398</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>73439.718</t>
+          <t>-74824.7140269733</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>71921.899</t>
+          <t>15373.1343535678</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>71614.043</t>
+          <t>150377.948174801</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>71455.053</t>
+          <t>68523.4309124809</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>75213.365</t>
+          <t>94704.572680633</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>77972.882</t>
+          <t>121895.345194769</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>133992.804</t>
+          <t>-40811997514.7545</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>54046.609</t>
+          <t>-14515712167.8026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>58890.544</t>
+          <t>-23303226441.3856</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61310.881</t>
+          <t>-23962123872.0038</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>64008.595</t>
+          <t>-30902311495.5723</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>70615.696</t>
+          <t>-37508564728.1933</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>77758.025</t>
+          <t>-44622798826.0057</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>85367.805</t>
+          <t>-46165324165.9222</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>82625.922</t>
+          <t>-39282636266.5312</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>96330.056</t>
+          <t>-54020562911.195</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>101655.09</t>
+          <t>-55388427175.1381</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>110703.37</t>
+          <t>-59967891832.7585</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>120494.884</t>
+          <t>-51038919672.3321</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>142146.868</t>
+          <t>-76306710407.7603</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>137543.405</t>
+          <t>-73786817574.5106</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>141049.985</t>
+          <t>-67673471004.2221</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>147507.943</t>
+          <t>-69864249437.0073</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>157465.824</t>
+          <t>-81618365339.7826</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>159755.098</t>
+          <t>-88603141713.7439</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>147314.349</t>
+          <t>-79502551327.0142</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>138623.74</t>
+          <t>-75830560429.2759</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>140161.697</t>
+          <t>-85466066283.2047</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>141269.29</t>
+          <t>-90736304477.3128</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>142335.19</t>
+          <t>-90558229847.9538</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>138147.787</t>
+          <t>-88348501085.9772</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>156871</t>
+          <t>-97291549237.7763</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>158601.141</t>
+          <t>-92589177195.1235</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>235870.906038897</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>269358.775743716</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>305066.253302261</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>276405.76827216</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.498</t>
+          <t>335421.191378367</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>445808.470786346</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>463351.353597877</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>459265.943374337</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>419528.677500565</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>449442.848601699</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>557485.697809314</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.041</t>
+          <t>639280.990994393</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.169</t>
+          <t>703113.602621513</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>822557.271496152</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.347</t>
+          <t>758563.079736656</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>929308.497577499</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1.733</t>
+          <t>1094419.47280386</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2.041</t>
+          <t>1258313.20632591</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2.013</t>
+          <t>1203943.45650037</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1.907</t>
+          <t>1207711.50477918</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>2.004</t>
+          <t>1212771.97843966</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>1.839</t>
+          <t>1200209.08960342</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>1.945</t>
+          <t>1238598.88402741</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>1.904</t>
+          <t>1318801.33482388</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1.955</t>
+          <t>1513127.75931093</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2.115</t>
+          <t>1524232.89124972</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>2.098</t>
+          <t>1568804.02898978</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>72492.798</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>30750.464</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>30958.981</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>31339.598</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>30274.658</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>31682.124</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30866.674</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>37239.448</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>37526.16</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>41553.192</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>44402.189</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>47950.534</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>55931.182</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>59465.535</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>59325.882</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>62826.284</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>62725.398</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>62820.324</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>64890.309</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>60763.928</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>57321.816</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>58342.618</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>57165.263</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>58188.081</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>60216.742</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>65805.008</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>68412.58</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>255245.846764154</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>291093.547545846</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>343314.231995681</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>352071.900588755</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>378859.228048395</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>484284.353972462</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>467214.040229358</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>514942.364266447</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>456175.70764792</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>471018.58243147</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>563827.04919024</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>647876.982359182</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>716401.12059125</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>812526.729264591</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>816280.759611454</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>971632.687539123</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>1089461.28811001</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>1264063.82549927</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>1230513.80275352</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>1247351.03652409</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>1403211.50811401</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>1422490.4326512</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>1444117.81854248</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>1485963.01922653</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>1696328.73696081</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>1745315.19325189</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.905</t>
+          <t>1794215.18906869</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>56390.813</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>18818.687</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>24133.851</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>25328.209</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>27731.617</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>34512.484</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>34108.188</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>41672.086</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>40195.039</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>48769.626</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>54064.498</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>56889.984</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>53512.486</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>67633.663</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>66404.216</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>63117.276</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>66322.48</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>72353.126</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>79376.412</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>67445.221</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>65216.701</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>72720.449</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>76365.194</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>81377.446</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>75184.951</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>86949.997</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>86841.98</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>38.13</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>12.9</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-7.84</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-11.64</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-17.39</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-31.13</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-39.87</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-44.48</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-40.86</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-47.43</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-48.53</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-53.69</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>-45.44</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>-49.04</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-45.07</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-41.22</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-36.52</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-36.32</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-38.23</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>6.46</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>5.56</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>-5.82</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>-12</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>-4.96</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>-13.5</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>-10.21</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>4627966.884</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>12.364</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>11.413</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>12.047</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>11.901</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>9.415</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>9.702</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>10.888</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>11.95</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>12.959</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>11.134</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>11.489</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>11.137</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>11.484</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>11.875</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>9.038</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>8.139</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>8.303</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>8.036</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>514327.289</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>426739.672</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>512208.017</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>521603.511</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>526227.751</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>455027.441</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>509119.037</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>507651.229</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>156636.64112792</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>180753.259807777</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>212327.572853</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>204130.157762426</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>240473.49610696</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>316610.22457431</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>349693.122806381</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>310062.050339347</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>271977.394515853</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>306035.24742167</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>379245.263160019</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>453935.998605451</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>485071.309629133</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>576427.618292048</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>532590.60762019</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>668014.071406599</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>801858.719509382</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>940212.134723114</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>920265.020303004</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>871747.671406476</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>862245.728564387</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>832576.156217367</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>881363.515000784</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>948740.067513928</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>1055526.25390125</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>1090069.43977089</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>1119391.3009062</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>77892274269.6009</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>21246000000.006</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>22241999999.9994</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>22380000000.0017</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>22907999999.9897</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>23768999999.988</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20507999999.9896</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>23137000000.0103</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>23772000000.0106</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>25638000000.0052</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>27825999999.9928</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>26344000000.01</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>29198999999.9813</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>34462999999.9965</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>36474000000.0228</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>37099999999.9853</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>42099999999.9756</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>46073000000.0049</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>49031000000.0401</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>71800384352.8648</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>68839622036.7767</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>73439717801.6763</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>71921898659.8856</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>71614042506.9382</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>71455052515.8536</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>75213365262.1358</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>77972882406.0216</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>116851919394.413</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>52254000000.011</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>52922000000.0035</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>54506000000.0109</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>55141999999.9973</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>55951000000.0028</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>51431999999.9928</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>57254999999.9932</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>61680000000.0178</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>67063999999.9967</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>72206000000.0016</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>74872000000.0015</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>87938999999.9931</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>93569000000.0166</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>92014000000.0256</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>99306000000.0111</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>101399999999.96</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>102375000000.007</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>104591000000.02</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>98166866239.6902</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>93174021172.3097</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>101909566630.01</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>100128782875.285</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>99892367514.3548</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>100251706101.657</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>108258277152.907</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>112688485131.496</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>72492797702.0372</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>30750463715.6797</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>30958981400.4419</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>31339597802.2018</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>30274657789.4146</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>31682123766.1293</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>30866673740.268</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>37239448392.1099</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>37526160070.6914</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>41553192289.9087</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>44402189097.179</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>47950534304.4174</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>55931181565.9988</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>59465535152.1654</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>59325881995.4232</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>62826284098.3674</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>62725398158.2494</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>62820324439.7946</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>64890308507.2168</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>60763928171.8191</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>57321816152.9635</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>58342617924.959</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>57165263402.1823</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>58188080932.1679</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>60216742148.0575</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>65805007788.5883</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>68412580028.8597</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>44740182.2627692</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>19412199.9999909</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>19676299.9999981</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>20429999.9999986</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20668200.0000029</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>20901599.9999948</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>19460300.0000056</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>21311800.0000055</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>23276100.0000046</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>25283100.0000006</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>26457200.0000033</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>27778200.000002</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>31411699.9999962</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>34684700.0000032</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>35387500.0000128</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>36984799.9999911</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>38410900.0000081</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>38705799.9999978</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>39170000.0000051</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>36800172.5746044</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>34861932.4069963</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>38189616.0760536</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>37360628.5767495</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>37248094.2997875</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>37591491.7470502</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>41005610.5684441</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>42729332.0311593</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>28688129.9306861</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>7840199.99998846</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>8194299.99999937</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>14264999.9999962</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>8292200.00000747</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>14784599.9999933</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>13358300.0000061</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>14829800.0000056</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>15889100.0000053</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>17163100.0000024</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>18043200.0000043</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>18441200.0000082</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>20263699.9999954</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>22945700.0000094</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>23956500.0000125</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>24559799.9999999</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>26507899.9999998</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>27380799.9999996</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>28029000.0000068</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>26144289.2801435</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>24956262.1704564</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26484695.2902657</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>25907276.4164936</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>25784251.9985426</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>25930789.4779931</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>27466607.5592235</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>28540592.8878475</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>116851919394.413</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>52254000000.011</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>52922000000.0035</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>54506000000.0109</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>55141999999.9973</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>55951000000.0028</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>51431999999.9928</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>57254999999.9932</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>61680000000.0178</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>67063999999.9967</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>72206000000.0016</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>74872000000.0015</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>87938999999.9931</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>93569000000.0166</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>92014000000.0256</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>99306000000.0111</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>101399999999.96</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>102375000000.007</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>104591000000.02</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>98166866239.6902</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>93174021172.3097</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>101909566630.01</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>100128782875.285</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>99892367514.3548</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>100251706101.657</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>108258277152.907</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>112688485131.496</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>77892274269.6009</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>21246000000.006</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>22241999999.9994</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>22380000000.0017</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>22907999999.9897</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>23768999999.988</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20507999999.9896</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>23137000000.0103</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>23772000000.0106</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>25638000000.0052</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>27825999999.9928</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>26344000000.01</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>29198999999.9813</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>34462999999.9965</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>36474000000.0228</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>37099999999.9853</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>42099999999.9756</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>46073000000.0049</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>49031000000.0401</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>71800384352.8648</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>68839622036.7767</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>73439717801.6763</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>71921898659.8856</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>71614042506.9382</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>71455052515.8536</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>75213365262.1358</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>77972882406.0216</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>927171.471369134</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1060382.4283977</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1216578.66381858</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1211720.46859424</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1345646.26741676</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1764921.08356962</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1861668.8074637</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1815695.13993229</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1602488.43833072</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1718442.32556649</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2074870.85044044</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2417327.78295331</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2691088.33399205</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>3108254.54895304</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2998512.84610092</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>3651851.18284709</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>4291708.08849593</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>4904685.39281939</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>4737094.04851311</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>4672524.39698447</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>5030101.57613283</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>5083182.66411794</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>5244465.09462974</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>5459209.94288293</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>5980382.04561112</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>6317059.74301751</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>6436101.819544</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>377818.048363014</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>435384.031198241</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>500955.078108746</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>494603.551452046</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>556895.418195371</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>713329.189382971</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>711453.360283611</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>742664.599163248</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>668074.773620159</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>701203.827012395</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>844401.869962787</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>974367.124226305</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1074123.53137698</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1234588.65050334</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1214528.10678077</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1467011.1006295</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1669174.13656473</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1941283.18377248</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1884127.50804715</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1907020.96190876</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>2075848.63700445</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>2079727.87332559</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2119179.48890612</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>2198042.00057435</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2512917.14067812</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>2568200.82702584</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>2642209.93503747</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3609,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3632,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3673,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4034,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
